--- a/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 8,98</t>
+          <t>-7,72; 8,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 4,71</t>
+          <t>-7,6; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,56</t>
+          <t>-1,15; 11,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 5,71</t>
+          <t>-2,88; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 4,75</t>
+          <t>-8,24; 4,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -1,65</t>
+          <t>-15,08; -1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 10,01</t>
+          <t>-3,23; 10,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -1,86</t>
+          <t>-15,69; -1,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,67</t>
+          <t>-1,09; 5,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,55</t>
+          <t>-4,01; 1,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,67</t>
+          <t>-2,77; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 504,44</t>
+          <t>-44,35; 560,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 138,99</t>
+          <t>-87,85; 117,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 351,06</t>
+          <t>-87,21; 352,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 8,61</t>
+          <t>-8,16; 9,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,45</t>
+          <t>-7,45; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 11,12</t>
+          <t>-0,39; 10,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,75</t>
+          <t>-3,27; 5,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 4,82</t>
+          <t>-11,12; 4,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -1,64</t>
+          <t>-16,13; -1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 10,06</t>
+          <t>-3,29; 9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -1,83</t>
+          <t>-14,32; -1,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,01</t>
+          <t>-1,44; 5,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,39</t>
+          <t>-3,71; 1,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,63</t>
+          <t>-3,06; 1,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 560,33</t>
+          <t>-57,47; 388,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 117,43</t>
+          <t>-86,19; 118,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 352,95</t>
+          <t>-89,78; 418,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 9,63</t>
+          <t>-7,7; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,0</t>
+          <t>-7,7; 4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,39</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,81</t>
+          <t>-0,1; 10,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,47</t>
+          <t>-3,3; 5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 4,78</t>
+          <t>-10,85; 4,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -1,64</t>
+          <t>-15,22; -1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,02</t>
+          <t>-3,25; 10,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -1,82</t>
+          <t>-15,89; -1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,11</t>
+          <t>-0,97; 5,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,37</t>
+          <t>-3,57; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,51</t>
+          <t>-2,69; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 388,41</t>
+          <t>-42,38; 504,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 118,52</t>
+          <t>-83,39; 138,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-89,78; 418,88</t>
+          <t>-88,19; 351,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-17,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0.371227206773468</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.346192784677926</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4657672456798365</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.3374016902860259</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2229418627242151</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,118 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 8,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 4,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.746616979017425</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.118323142705481</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.659520807632417</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.61592916610493</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.682926334488333</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>321,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,1; 10,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 5,71</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,65</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0.6592307699805464</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2062188007108176</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5337233344982261</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2.58423093353648</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3908475490646033</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.2535779122159946</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.7792263216414935</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,85; 4,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-15,22; -1,65</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.800531351740919</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.782410273582975</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.870790060807264</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +747,215 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.04446301109379069</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.484182729218786</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.09720263067265536</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,25; 10,01</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,89; -1,86</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.387878771529495</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-3.701313624697012</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8423687009293382</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>-0.373714876137065</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.09687206119715661</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.059710526539512</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3115109825998554</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.3108618074286035</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6239426720153151</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.849387947718003</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.384508883358442</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.3371374954746226</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.735599597173141</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-35,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-25,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 5,67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,57; 1,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-42,38; 504,44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-83,39; 138,99</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-88,19; 351,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.3103423196200105</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.2504567071346651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.05253578108600039</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.6854163619975722</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3371196004354387</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1398155768639447</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.2931731909522857</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.9310440924440256</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5858416377280756</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.523641314510919</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8673957106887953</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9108660836075521</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.386916849020458</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3923913423397534</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5.302899561701142</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.430324878230701</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.381147932873942</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +964,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
